--- a/data/sxbet/ligas/The Championship/trades.xlsx
+++ b/data/sxbet/ligas/The Championship/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,110 +531,862 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>44.18</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.3162</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19292114</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1786621774</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>139.699605</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>19.99999</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.7437</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19292114</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1786619915</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>26.890743</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.4863</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sheffield United FC vs Birmingham</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sheffield United FC</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19291904</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1786615902</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1786811400</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>16.781491</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>50.81</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.4575</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Stoke City vs Swansea City</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19291703</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1786609224</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>111.060109</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.3692</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.3675</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1786606182</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3.725714</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>14.31</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.8662</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1786593406</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>16.519481</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12.51999</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.675</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1786593405</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>18.548133</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>0x70c4d883377e0e7a1da0f5a54162f0682a7a75df864f08a0d9215d9bc3d1bb50</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>4.99998</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>The Championship</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>0x0f77092bad3391e566ab01befe9ffbf1d0769f5d84eb4679b9515f28bed1fe92</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>L19292126</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1786496850</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>1786734000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>6.410231</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/The Championship/trades.xlsx
+++ b/data/sxbet/ligas/The Championship/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,102 +531,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
+          <t>0xd52581c04ad82aa50dd0e5fd34c05139f4741fac293b4131701be67fa1f4e9fd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>29.57257</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.495</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>44.18</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.3162</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>L19292114</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786621774</t>
+          <t>1786637737</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>139.699605</t>
+          <t>59.742566</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,102 +635,94 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
+          <t>0x830f9a73e2c448c31ca55665eabaac552ea63303de6c11ee3218137ca19171c3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>22.81</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.4975</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>19.99999</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.7437</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>L19292114</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786619915</t>
+          <t>1786636199</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>26.890743</t>
+          <t>45.849246</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,102 +739,94 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
+          <t>0xe3095a8d8520173ca9ca0e37b8915f9befbcf19766b6d15861b56a62fd451312</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>15.37331</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.1912</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>8.16</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.4863</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sheffield United FC vs Birmingham</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Sheffield United FC</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Birmingham</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>L19291904</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786615902</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786811400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>16.781491</t>
+          <t>80.38332</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,28 +843,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
+          <t>0xd6836273ea70f65f0163c9825f8b5f82c746330452f7d9529c96a87e10fde671</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>50.81</t>
+          <t>53.10381</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4575</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -899,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Stoke City vs Swansea City</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19291703</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786609224</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>111.060109</t>
+          <t>143.523811</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,28 +947,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
+          <t>0x9b861e3a5951a5bc4a795bbd4936d267f07999dfdbc8680041a8afb95a853d63</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.3692</t>
+          <t>15.37331</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.1912</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>The Championship</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1018,7 +994,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x6c28e6d44aba4a5c5135538948c11f026030c3793c5b485a1fddac009874d97c</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786606182</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.725714</t>
+          <t>80.38332</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,28 +1051,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
+          <t>0x4c8f7a1fd16abd3821389519299c565b87c1cfc798c8f40cba30cb98d1cb3a8e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.8662</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1107,27 +1083,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1128,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786593406</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>16.519481</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1155,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+          <t>0x29a09089970963ba620d5e0ec4f16a2c200278f6312c796968ef3083a5788664</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1187,15 +1163,19 @@
           <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.51999</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1203,7 +1183,11 @@
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -1211,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Portsmouth vs Queens Park Rangers</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+          <t>0x434e450484615c8151c89575c12a656ce79bf52c262db30f4d9d1711975a5a43</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19292114</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786593405</t>
+          <t>1786629015</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786802400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>18.548133</t>
+          <t>38.358974</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,110 +1267,1070 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>0x537be368ed5c10f96c004f82bf70d830d895e83a27d307988ebb471734297180</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>15.15832</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.4925</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1786625324</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>30.778315</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0x0baa6a9ec22c5ea443e8ee1130a9e8d7d9b9fa0084f51b5e1ee100ac5168a69d</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>42.72887</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.6212</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1786625324</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>68.778865</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>44.18</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.3162</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19292114</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1786621774</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>139.699605</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>19.99999</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.7437</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19292114</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1786619915</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>26.890743</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.4863</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sheffield United FC vs Birmingham</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sheffield United FC</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19291904</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1786615902</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1786811400</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>16.781491</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>50.81</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.4575</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Stoke City vs Swansea City</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19291703</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1786609224</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>111.060109</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.3692</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.3675</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1786606182</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3.725714</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>14.31</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.8662</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1786593406</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>16.519481</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>12.51999</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.675</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1786593405</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>18.548133</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>0x70c4d883377e0e7a1da0f5a54162f0682a7a75df864f08a0d9215d9bc3d1bb50</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>4.99998</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>The Championship</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0x0f77092bad3391e566ab01befe9ffbf1d0769f5d84eb4679b9515f28bed1fe92</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>L19292126</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>1786496850</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1786734000</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>6.410231</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/The Championship/trades.xlsx
+++ b/data/sxbet/ligas/The Championship/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd52581c04ad82aa50dd0e5fd34c05139f4741fac293b4131701be67fa1f4e9fd</t>
+          <t>0x1ca5645b840e0099c37a192c12665c34258dca551f75cca08585650a1b8119c5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.57257</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4663</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786637737</t>
+          <t>1786654867</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>59.742566</t>
+          <t>22.841823</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +635,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x830f9a73e2c448c31ca55665eabaac552ea63303de6c11ee3218137ca19171c3</t>
+          <t>0xf866368b051fe0cbdd3da4934c3bc39714b17f0249c765c085c864368ae0c2d9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>10.59988</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -2</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786636199</t>
+          <t>1786651979</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>45.849246</t>
+          <t>47.63991</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +747,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe3095a8d8520173ca9ca0e37b8915f9befbcf19766b6d15861b56a62fd451312</t>
+          <t>0xa30b5de275cc97dc98ab7b990de9244cc76a5cd746f5e91690bc2938ce24c906</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.37331</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1912</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786651979</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>80.38332</t>
+          <t>7.367742</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd6836273ea70f65f0163c9825f8b5f82c746330452f7d9529c96a87e10fde671</t>
+          <t>0xd52581c04ad82aa50dd0e5fd34c05139f4741fac293b4131701be67fa1f4e9fd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,17 +862,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>53.10381</t>
+          <t>29.57257</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -890,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -920,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786637737</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>143.523811</t>
+          <t>59.742566</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +955,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x9b861e3a5951a5bc4a795bbd4936d267f07999dfdbc8680041a8afb95a853d63</t>
+          <t>0x830f9a73e2c448c31ca55665eabaac552ea63303de6c11ee3218137ca19171c3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15.37331</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.1912</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -994,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x6c28e6d44aba4a5c5135538948c11f026030c3793c5b485a1fddac009874d97c</t>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1024,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786636199</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>80.38332</t>
+          <t>45.849246</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,7 +1059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x4c8f7a1fd16abd3821389519299c565b87c1cfc798c8f40cba30cb98d1cb3a8e</t>
+          <t>0xe3095a8d8520173ca9ca0e37b8915f9befbcf19766b6d15861b56a62fd451312</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1062,17 +1070,17 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>15.37331</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>The Championship</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1098,7 +1106,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1138,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>80.38332</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,102 +1163,94 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x29a09089970963ba620d5e0ec4f16a2c200278f6312c796968ef3083a5788664</t>
+          <t>0xd6836273ea70f65f0163c9825f8b5f82c746330452f7d9529c96a87e10fde671</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>53.10381</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1.3413</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0x434e450484615c8151c89575c12a656ce79bf52c262db30f4d9d1711975a5a43</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>L19292114</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786629015</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>38.358974</t>
+          <t>143.523811</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x537be368ed5c10f96c004f82bf70d830d895e83a27d307988ebb471734297180</t>
+          <t>0x9b861e3a5951a5bc4a795bbd4936d267f07999dfdbc8680041a8afb95a853d63</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1278,17 +1278,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15.15832</t>
+          <t>15.37331</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.1912</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>The Championship</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0x6c28e6d44aba4a5c5135538948c11f026030c3793c5b485a1fddac009874d97c</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786625324</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>30.778315</t>
+          <t>80.38332</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x0baa6a9ec22c5ea443e8ee1130a9e8d7d9b9fa0084f51b5e1ee100ac5168a69d</t>
+          <t>0x4c8f7a1fd16abd3821389519299c565b87c1cfc798c8f40cba30cb98d1cb3a8e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1382,17 +1382,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.72887</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786625324</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>68.778865</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,12 +1475,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
+          <t>0x29a09089970963ba620d5e0ec4f16a2c200278f6312c796968ef3083a5788664</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1490,47 +1490,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>Queens Park Rangers</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Queens Park Rangers</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
+          <t>0x434e450484615c8151c89575c12a656ce79bf52c262db30f4d9d1711975a5a43</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786621774</t>
+          <t>1786629015</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>139.699605</t>
+          <t>38.358974</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,102 +1587,94 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
+          <t>0x537be368ed5c10f96c004f82bf70d830d895e83a27d307988ebb471734297180</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>15.15832</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.4925</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>19.99999</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1.7437</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>L19292114</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786619915</t>
+          <t>1786625324</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>26.890743</t>
+          <t>30.778315</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,102 +1691,94 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
+          <t>0x0baa6a9ec22c5ea443e8ee1130a9e8d7d9b9fa0084f51b5e1ee100ac5168a69d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>42.72887</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.6212</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8.16</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1.4863</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Sheffield United FC vs Birmingham</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Sheffield United FC</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Birmingham</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>L19291904</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786615902</t>
+          <t>1786625324</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786811400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>16.781491</t>
+          <t>68.778865</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,7 +1795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
+          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1819,51 +1803,59 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>50.81</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4575</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>The Championship</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Stoke City vs Swansea City</t>
+          <t>Portsmouth vs Queens Park Rangers</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
+          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19291703</t>
+          <t>L19292114</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1888,7 +1880,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786609224</t>
+          <t>1786621774</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1890,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>111.060109</t>
+          <t>139.699605</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,31 +1907,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
+          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.3692</t>
+          <t>19.99999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -1947,27 +1947,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+          <t>Portsmouth vs Queens Park Rangers</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19292126</t>
+          <t>L19292114</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1992,17 +1992,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786606182</t>
+          <t>1786619915</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786734000</t>
+          <t>1786802400</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>3.725714</t>
+          <t>26.890743</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,31 +2019,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
+          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8662</t>
+          <t>1.4863</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -2051,27 +2059,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Sheffield United FC vs Birmingham</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheffield United FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
+          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19291904</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2096,17 +2104,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786593406</t>
+          <t>1786615902</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786811400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>16.519481</t>
+          <t>16.781491</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,28 +2131,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.51999</t>
+          <t>50.81</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.4575</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>The Championship</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2155,27 +2163,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Stoke City vs Swansea City</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19291703</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2200,17 +2208,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786593405</t>
+          <t>1786609224</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786802400</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>18.548133</t>
+          <t>111.060109</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,110 +2235,422 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.3692</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.3675</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1786606182</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3.725714</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>14.31</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.8662</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1786593406</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>16.519481</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>12.51999</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.675</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1786593405</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>18.548133</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>0x70c4d883377e0e7a1da0f5a54162f0682a7a75df864f08a0d9215d9bc3d1bb50</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>4.99998</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>The Championship</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>0x0f77092bad3391e566ab01befe9ffbf1d0769f5d84eb4679b9515f28bed1fe92</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>L19292126</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>1786496850</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>1786734000</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>6.410231</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/The Championship/trades.xlsx
+++ b/data/sxbet/ligas/The Championship/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x1ca5645b840e0099c37a192c12665c34258dca551f75cca08585650a1b8119c5</t>
+          <t>0x0eed25f538f3923c390dcdeb951387eab37a7b6903d2ff32be765d4c2b578176</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>62.24994</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4663</t>
+          <t>1.8562</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786654867</t>
+          <t>1786672368</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>22.841823</t>
+          <t>72.70066</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf866368b051fe0cbdd3da4934c3bc39714b17f0249c765c085c864368ae0c2d9</t>
+          <t>0x1ca5645b840e0099c37a192c12665c34258dca551f75cca08585650a1b8119c5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,84 +643,76 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.4663</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>10.59988</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.2225</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers -2</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>L19292126</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786651979</t>
+          <t>1786654867</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>47.63991</t>
+          <t>22.841823</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xa30b5de275cc97dc98ab7b990de9244cc76a5cd746f5e91690bc2938ce24c906</t>
+          <t>0xf866368b051fe0cbdd3da4934c3bc39714b17f0249c765c085c864368ae0c2d9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -755,15 +747,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>10.59988</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -771,7 +767,11 @@
           <t>Asian Handicap (-2)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -2</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>7.367742</t>
+          <t>47.63991</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +851,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd52581c04ad82aa50dd0e5fd34c05139f4741fac293b4131701be67fa1f4e9fd</t>
+          <t>0xa30b5de275cc97dc98ab7b990de9244cc76a5cd746f5e91690bc2938ce24c906</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29.57257</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786637737</t>
+          <t>1786651979</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>59.742566</t>
+          <t>7.367742</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,23 +955,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x830f9a73e2c448c31ca55665eabaac552ea63303de6c11ee3218137ca19171c3</t>
+          <t>0xd52581c04ad82aa50dd0e5fd34c05139f4741fac293b4131701be67fa1f4e9fd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>29.57257</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786636199</t>
+          <t>1786637737</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>45.849246</t>
+          <t>59.742566</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,28 +1059,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xe3095a8d8520173ca9ca0e37b8915f9befbcf19766b6d15861b56a62fd451312</t>
+          <t>0x830f9a73e2c448c31ca55665eabaac552ea63303de6c11ee3218137ca19171c3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.37331</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1912</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786636199</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>80.38332</t>
+          <t>45.849246</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xd6836273ea70f65f0163c9825f8b5f82c746330452f7d9529c96a87e10fde671</t>
+          <t>0xe3095a8d8520173ca9ca0e37b8915f9befbcf19766b6d15861b56a62fd451312</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1174,17 +1174,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>53.10381</t>
+          <t>15.37331</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.1912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>The Championship</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>143.523811</t>
+          <t>80.38332</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x9b861e3a5951a5bc4a795bbd4936d267f07999dfdbc8680041a8afb95a853d63</t>
+          <t>0xd6836273ea70f65f0163c9825f8b5f82c746330452f7d9529c96a87e10fde671</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1278,17 +1278,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15.37331</t>
+          <t>53.10381</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1912</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x6c28e6d44aba4a5c5135538948c11f026030c3793c5b485a1fddac009874d97c</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>80.38332</t>
+          <t>143.523811</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x4c8f7a1fd16abd3821389519299c565b87c1cfc798c8f40cba30cb98d1cb3a8e</t>
+          <t>0x9b861e3a5951a5bc4a795bbd4936d267f07999dfdbc8680041a8afb95a853d63</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1382,17 +1382,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>15.37331</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.1912</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>The Championship</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0x6c28e6d44aba4a5c5135538948c11f026030c3793c5b485a1fddac009874d97c</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>80.38332</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,102 +1475,94 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x29a09089970963ba620d5e0ec4f16a2c200278f6312c796968ef3083a5788664</t>
+          <t>0x4c8f7a1fd16abd3821389519299c565b87c1cfc798c8f40cba30cb98d1cb3a8e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>27.01</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.3413</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0x434e450484615c8151c89575c12a656ce79bf52c262db30f4d9d1711975a5a43</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>L19292114</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786629015</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38.358974</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,31 +1579,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x537be368ed5c10f96c004f82bf70d830d895e83a27d307988ebb471734297180</t>
+          <t>0x29a09089970963ba620d5e0ec4f16a2c200278f6312c796968ef3083a5788664</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.15832</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -1619,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+          <t>Portsmouth vs Queens Park Rangers</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0x434e450484615c8151c89575c12a656ce79bf52c262db30f4d9d1711975a5a43</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19292126</t>
+          <t>L19292114</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1664,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786625324</t>
+          <t>1786629015</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786734000</t>
+          <t>1786802400</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>30.778315</t>
+          <t>38.358974</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,7 +1691,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x0baa6a9ec22c5ea443e8ee1130a9e8d7d9b9fa0084f51b5e1ee100ac5168a69d</t>
+          <t>0x537be368ed5c10f96c004f82bf70d830d895e83a27d307988ebb471734297180</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1702,17 +1702,17 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>42.72887</t>
+          <t>15.15832</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>68.778865</t>
+          <t>30.778315</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,102 +1795,94 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
+          <t>0x0baa6a9ec22c5ea443e8ee1130a9e8d7d9b9fa0084f51b5e1ee100ac5168a69d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>42.72887</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.6212</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>44.18</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1.3162</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Queens Park Rangers</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>L19292114</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786621774</t>
+          <t>1786625324</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>139.699605</t>
+          <t>68.778865</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1907,12 +1899,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
+          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1922,22 +1914,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19.99999</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1962,7 +1954,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
+          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1992,7 +1984,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786619915</t>
+          <t>1786621774</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2002,7 +1994,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>26.890743</t>
+          <t>139.699605</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,12 +2011,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
+          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2034,22 +2026,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>19.99999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4863</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2059,27 +2051,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sheffield United FC vs Birmingham</t>
+          <t>Portsmouth vs Queens Park Rangers</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sheffield United FC</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
+          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19291904</t>
+          <t>L19292114</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2104,17 +2096,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786615902</t>
+          <t>1786619915</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786811400</t>
+          <t>1786802400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>16.781491</t>
+          <t>26.890743</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2131,7 +2123,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
+          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2139,51 +2131,59 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>50.81</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4575</t>
+          <t>1.4863</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>The Championship</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Stoke City vs Swansea City</t>
+          <t>Sheffield United FC vs Birmingham</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield United FC</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
+          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19291703</t>
+          <t>L19291904</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786609224</t>
+          <t>1786615902</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786811400</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>111.060109</t>
+          <t>16.781491</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,28 +2235,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
+          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.3692</t>
+          <t>50.81</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.4575</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>The Championship</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2267,27 +2267,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+          <t>Stoke City vs Swansea City</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19292126</t>
+          <t>L19291703</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2312,17 +2312,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786606182</t>
+          <t>1786609224</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786734000</t>
+          <t>1786802400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3.725714</t>
+          <t>111.060109</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2339,28 +2339,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
+          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>1.3692</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.8662</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2371,27 +2371,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786593406</t>
+          <t>1786606182</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>16.519481</t>
+          <t>3.725714</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,7 +2443,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2454,17 +2454,17 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12.51999</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.8662</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786593405</t>
+          <t>1786593406</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>18.548133</t>
+          <t>16.519481</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2547,110 +2547,214 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>12.51999</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.675</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1786593405</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>18.548133</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>0x70c4d883377e0e7a1da0f5a54162f0682a7a75df864f08a0d9215d9bc3d1bb50</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>4.99998</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>The Championship</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>0x0f77092bad3391e566ab01befe9ffbf1d0769f5d84eb4679b9515f28bed1fe92</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>L19292126</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>1786496850</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>1786734000</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>6.410231</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/The Championship/trades.xlsx
+++ b/data/sxbet/ligas/The Championship/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0eed25f538f3923c390dcdeb951387eab37a7b6903d2ff32be765d4c2b578176</t>
+          <t>0xeef7fdbc6f623362f5b22e9e9851b55a649d3b22d0629618d0399282d976f0f7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>62.24994</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.8562</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786672368</t>
+          <t>1786690757</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>72.70066</t>
+          <t>71.181102</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x1ca5645b840e0099c37a192c12665c34258dca551f75cca08585650a1b8119c5</t>
+          <t>0xc0f59f7d4f680f2d6c4b15af9fcd33bb40013b8c7213edb06034ffaef8155d62</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4663</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>The Championship</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+          <t>Portsmouth vs Queens Park Rangers</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xb99abb250b0a6f0129b96f76d74fe24be9e0456e3abe6efb79a30a4b3661122d</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19292126</t>
+          <t>L19292114</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786654867</t>
+          <t>1786690728</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786734000</t>
+          <t>1786802400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>22.841823</t>
+          <t>75.83908</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,12 +739,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xf866368b051fe0cbdd3da4934c3bc39714b17f0249c765c085c864368ae0c2d9</t>
+          <t>0x42cc47860d900e2d7e2e19c627d9d9c7d526f0d1557d86261e5d406bdbf99d46</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -754,22 +754,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.59988</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers -2</t>
+          <t>Wolverhampton Wanderers -0.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786651979</t>
+          <t>1786688827</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>47.63991</t>
+          <t>7.905123</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,31 +851,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xa30b5de275cc97dc98ab7b990de9244cc76a5cd746f5e91690bc2938ce24c906</t>
+          <t>0x8464d57be33ce2f55c677d3da202780847ffdd85c3dfa6a6d80d7ce815105a8c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>31.11999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.6288</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -0.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -898,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786651979</t>
+          <t>1786688817</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>7.367742</t>
+          <t>49.495014</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xd52581c04ad82aa50dd0e5fd34c05139f4741fac293b4131701be67fa1f4e9fd</t>
+          <t>0x4667207193cd8c05799c41113eb3fa010abded418c33fb0563c7153e21568351</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -963,23 +971,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29.57257</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.3925</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -1002,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786637737</t>
+          <t>1786688805</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>59.742566</t>
+          <t>35.057325</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,28 +1075,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x830f9a73e2c448c31ca55665eabaac552ea63303de6c11ee3218137ca19171c3</t>
+          <t>0xffdfff603d38c686381000bc91f069bb99d31cebdd19676da11cbf7b164f90f7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.6987</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1106,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786636199</t>
+          <t>1786688747</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>45.849246</t>
+          <t>49.159213</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,28 +1179,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe3095a8d8520173ca9ca0e37b8915f9befbcf19766b6d15861b56a62fd451312</t>
+          <t>0x33fde247c5c6973996e8b1fb864ad4efe889ffdbc2841d1b9afab2296d693194</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.37331</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.1912</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1210,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786688747</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>80.38332</t>
+          <t>35.313984</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,31 +1283,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd6836273ea70f65f0163c9825f8b5f82c746330452f7d9529c96a87e10fde671</t>
+          <t>0x56b12908d45a0a6d124c5eba50f10571c241cba2a831d338dd1abd9b46538145</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>53.10381</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -1314,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1344,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786688148</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>143.523811</t>
+          <t>19.46988</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9b861e3a5951a5bc4a795bbd4936d267f07999dfdbc8680041a8afb95a853d63</t>
+          <t>0xc7dd73efc8a2687272b80e45be086997d0a80191961ab64cecfa57daa1f2f22e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1382,17 +1406,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.37331</t>
+          <t>13.80271</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.1912</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1403,27 +1427,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+          <t>Bolton Wanderers vs Preston North End</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x6c28e6d44aba4a5c5135538948c11f026030c3793c5b485a1fddac009874d97c</t>
+          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19292126</t>
+          <t>L19291709</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1448,17 +1472,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786687562</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786734000</t>
+          <t>1786793400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>80.38332</t>
+          <t>21.032701</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,28 +1499,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x4c8f7a1fd16abd3821389519299c565b87c1cfc798c8f40cba30cb98d1cb3a8e</t>
+          <t>0x1fa03bf72cff6dce4d0ea2e6afe0c3c4d96e870ad881c829d4b280526f52994d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>48.6786</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.6362</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1522,7 +1546,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1552,7 +1576,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786687154</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1562,7 +1586,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.508605</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,39 +1603,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x29a09089970963ba620d5e0ec4f16a2c200278f6312c796968ef3083a5788664</t>
+          <t>0x2181f862594910f0be2837965261ee46675dcd94fd6477edde8e2ef6700a3620</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>28.93998</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3413</t>
+          <t>1.8525</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -1619,27 +1635,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x434e450484615c8151c89575c12a656ce79bf52c262db30f4d9d1711975a5a43</t>
+          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19292114</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1664,17 +1680,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786629015</t>
+          <t>1786686832</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>38.358974</t>
+          <t>33.947191</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,31 +1707,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x537be368ed5c10f96c004f82bf70d830d895e83a27d307988ebb471734297180</t>
+          <t>0x9a30cb693b24b6af0b636876c34b3721ed6c64f547308b4491fe3874711d6390</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15.15832</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -1738,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1768,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786625324</t>
+          <t>1786686792</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1778,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>30.778315</t>
+          <t>7.407407</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,31 +1819,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x0baa6a9ec22c5ea443e8ee1130a9e8d7d9b9fa0084f51b5e1ee100ac5168a69d</t>
+          <t>0x5cf303c4268c205c3900dd177e853e57be65f604c6cf2f75bb3ec158206319e8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xc1BEa02928E7Dbb4b88c093f3EFC8FEcdC54334f</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42.72887</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.2275</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -1842,7 +1874,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+          <t>0xe5ad076050ebf08633ea9b91bf5072f3d9a9f79b460dff0451eee48c48db08db</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1872,7 +1904,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786625324</t>
+          <t>1786686289</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1882,7 +1914,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>68.778865</t>
+          <t>186.813187</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,12 +1931,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
+          <t>0x85bc4c2b09a29cb7b51361cb6e00c779b54c2ba9aa0fa910571efb4334c34a34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1914,22 +1946,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.2188</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wolverhampton Wanderers -2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1939,27 +1971,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19292114</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1984,17 +2016,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786621774</t>
+          <t>1786684350</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>139.699605</t>
+          <t>46.354286</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,12 +2043,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
+          <t>0xe421855f5800b15e1ce538ac99e357340482a63f9eb53861728bf1fe6f5927ef</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2026,22 +2058,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19.99999</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.2188</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Wolverhampton Wanderers -2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2051,27 +2083,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19292114</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2096,17 +2128,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786619915</t>
+          <t>1786681813</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>26.890743</t>
+          <t>13.485714</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,39 +2155,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
+          <t>0xdfd3b0e87b38a21c6b6de5e710fa222376f415690d024b88ddc6ac78e8ffd6a2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>35.36889</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4863</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -2163,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sheffield United FC vs Birmingham</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sheffield United FC</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
+          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19291904</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2208,17 +2232,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786615902</t>
+          <t>1786681421</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786811400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>16.781491</t>
+          <t>59.318893</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,28 +2259,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
+          <t>0x90a0e7eda8f358bfbc693c5b170d49b5b82643edb5226d7baf7c5efb116e35f4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50.81</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4575</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2267,27 +2291,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Stoke City vs Swansea City</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19291703</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2312,17 +2336,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786609224</t>
+          <t>1786681421</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>111.060109</t>
+          <t>66.194093</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2339,28 +2363,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
+          <t>0xf07ac8a6314c65b6d3fa4324af4db0742f2b81142e826d79c02967ae2b680845</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.3692</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2386,7 +2410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2416,7 +2440,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786606182</t>
+          <t>1786681420</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2426,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3.725714</t>
+          <t>62.287263</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,28 +2467,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
+          <t>0xee5c5a9e51e535e869e916990033cb897db812220c0aac5432bf2226c3d7ee57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>48.17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.8662</t>
+          <t>1.7738</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2475,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2520,17 +2544,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786593406</t>
+          <t>1786681101</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>16.519481</t>
+          <t>62.25525</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2547,28 +2571,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+          <t>0x79e08f4bc06434a4f7979320414002d9965fb48cb9bc37896538f9f823d71572</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12.51999</t>
+          <t>18.73305</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2579,27 +2603,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2624,17 +2648,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786593405</t>
+          <t>1786681101</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>18.548133</t>
+          <t>29.913054</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2651,110 +2675,2446 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>0x1d5be24f030cf08ecf8f855e19663320ae258826d7bb9f9b58cb44aa00e0d704</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>52.2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.4963</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1786681101</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>105.188917</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x47a0705d873daff1b9735c7743adc7d7070905bee2a7f19cf8b07326af3af9ce</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22.33999</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.7138</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1786678335</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>31.299461</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0x0eed25f538f3923c390dcdeb951387eab37a7b6903d2ff32be765d4c2b578176</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>62.24994</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.8562</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1786672368</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>72.70066</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x1ca5645b840e0099c37a192c12665c34258dca551f75cca08585650a1b8119c5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.4663</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1786654867</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>22.841823</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0xf866368b051fe0cbdd3da4934c3bc39714b17f0249c765c085c864368ae0c2d9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>10.59988</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.2225</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -2</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1786651979</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>47.63991</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0xa30b5de275cc97dc98ab7b990de9244cc76a5cd746f5e91690bc2938ce24c906</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1786651979</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>7.367742</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0xd52581c04ad82aa50dd0e5fd34c05139f4741fac293b4131701be67fa1f4e9fd</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>29.57257</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.495</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1786637737</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>59.742566</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0x830f9a73e2c448c31ca55665eabaac552ea63303de6c11ee3218137ca19171c3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22.81</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.4975</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1786636199</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>45.849246</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0xe3095a8d8520173ca9ca0e37b8915f9befbcf19766b6d15861b56a62fd451312</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>15.37331</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.1912</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1786633531</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>80.38332</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0xd6836273ea70f65f0163c9825f8b5f82c746330452f7d9529c96a87e10fde671</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>53.10381</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1786633531</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>143.523811</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0x9b861e3a5951a5bc4a795bbd4936d267f07999dfdbc8680041a8afb95a853d63</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>15.37331</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.1912</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x6c28e6d44aba4a5c5135538948c11f026030c3793c5b485a1fddac009874d97c</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1786633531</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>80.38332</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x4c8f7a1fd16abd3821389519299c565b87c1cfc798c8f40cba30cb98d1cb3a8e</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>27.01</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1786633531</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x29a09089970963ba620d5e0ec4f16a2c200278f6312c796968ef3083a5788664</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>13.09</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.3413</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x434e450484615c8151c89575c12a656ce79bf52c262db30f4d9d1711975a5a43</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19292114</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1786629015</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>38.358974</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x537be368ed5c10f96c004f82bf70d830d895e83a27d307988ebb471734297180</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>15.15832</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.4925</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1786625324</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>30.778315</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x0baa6a9ec22c5ea443e8ee1130a9e8d7d9b9fa0084f51b5e1ee100ac5168a69d</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>42.72887</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.6212</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1786625324</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>68.778865</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>44.18</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.3162</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19292114</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1786621774</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>139.699605</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>19.99999</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.7437</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19292114</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1786619915</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>26.890743</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.4863</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sheffield United FC vs Birmingham</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sheffield United FC</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19291904</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1786615902</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1786811400</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>16.781491</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>50.81</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.4575</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Stoke City vs Swansea City</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19291703</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1786609224</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>111.060109</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.3692</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.3675</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1786606182</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3.725714</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>14.31</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.8662</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1786593406</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>16.519481</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>12.51999</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.675</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1786593405</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>18.548133</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>0x70c4d883377e0e7a1da0f5a54162f0682a7a75df864f08a0d9215d9bc3d1bb50</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>4.99998</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>The Championship</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>0x0f77092bad3391e566ab01befe9ffbf1d0769f5d84eb4679b9515f28bed1fe92</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>L19292126</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
         <is>
           <t>1786496850</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>1786734000</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>6.410231</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/The Championship/trades.xlsx
+++ b/data/sxbet/ligas/The Championship/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V121"/>
+  <dimension ref="A1:V129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0017526f3d1a6b806241fdcf270ec20ac55310303738ded60cf0ac60d200236b</t>
+          <t>0x3d2d7c958dd89ce448fe44f964c40feea6164c4a5ae2fe56f6a6589de79446bc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>156.00221</t>
+          <t>97.21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6313</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,26 +555,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786708851</t>
+          <t>1786712221</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>247.132214</t>
+          <t>260.966443</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,39 +635,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x941378707269e8ed5e06a95bc2d98721e8b7ff0eece34bc91f7e8dc6c73dac5d</t>
+          <t>0x2041b6b4eca8e7c4d586bf3fc7a83e62b0df27eb4ab5fb00d4ee4fa0d18812dc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.97366</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -683,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xaab7ad8955da3f0ebc21e85cb94db3fb6514c90829a10cc7307351506de926f4</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786708757</t>
+          <t>1786711631</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>92.253662</t>
+          <t>17.852349</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +739,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5eb46e0a523b14bdf2cc8cb4828842be713817190b52979b65224fc8dbb37674</t>
+          <t>0x8661eb854cdc4697da9c59d2228c91a45d611bfcabaa25f8fdf2d489dfb7b27a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xEf5d1AdDCb6404CDC4496B328c3B2e539b79530d</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,39 +754,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.42999</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Wolverhampton Wanderers -1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -810,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786708273</t>
+          <t>1786711497</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>5.47703</t>
+          <t>35.573201</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x44f734cd4ef52e63696612eaa384396228698b2f1c2377a4e06f63f581df1a74</t>
+          <t>0x02171f6924905f2f60c18bc933394da5697a8b6ced532492896214f5ded453e9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -882,39 +866,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>141.43332</t>
+          <t>7.96999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6338</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Wolverhampton Wanderers -0.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -922,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786708085</t>
+          <t>1786710924</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>224.497333</t>
+          <t>12.575921</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xe78d28ff133f41d789623e70ac3fd6613308d9fe8fa93e969c4bf85311232af7</t>
+          <t>0xf04511216255cc39cafbbaa2af4be826e9a1d959d3134983af490bd209477681</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -987,31 +971,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.71294</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -1034,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1064,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786708082</t>
+          <t>1786710779</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>12.242762</t>
+          <t>34.421875</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,39 +1067,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xc5b5004635526c466c918c6f01bbdbbe1365cb136cdd26badae6c2f34c094f49</t>
+          <t>0x2d4012f0b67d40a09ae80182eb3f2072c0c7ce6b0295f9628e62b743128cfe87</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18.61</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -1131,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+          <t>Bolton Wanderers vs Preston North End</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x486e2e235ef3fda3663e84fce83d1a06cf6dfa468f902e05afb6fb2b6296b066</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19292126</t>
+          <t>L19291709</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1176,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786708082</t>
+          <t>1786710712</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786734000</t>
+          <t>1786793400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>29.539683</t>
+          <t>11.079812</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,12 +1171,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x6a0a491d3af8142975c3b8281045f72534d93d1c9f4e7286ed87307ede890a58</t>
+          <t>0x1eb584add9668d274c53e04e04a0cedd1f4590c60ec456ea5ed0386291eacbd6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1218,39 +1186,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>102.98334</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -1258,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1288,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786708082</t>
+          <t>1786710319</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1298,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>164.773344</t>
+          <t>6.030151</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1315,7 +1283,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd0e875f15c46a885a411e00368a75be2fca469d70066f8fe002453a05e8246e9</t>
+          <t>0xf6d12293fa8e9e9ad6c4c7c2f1b9e706242cc6884b06948a9ffd925ce7add48c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1330,29 +1298,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18.45559</t>
+          <t>24.75862</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>The Championship</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers 0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
@@ -1370,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1400,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786708080</t>
+          <t>1786709998</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1410,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>26.178142</t>
+          <t>49.148625</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1427,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x1da64a71c2f3b4f5eb5c0de77dcfeba7a88a1a7dfcc7650ac6ed1c5faf61119d</t>
+          <t>0x0017526f3d1a6b806241fdcf270ec20ac55310303738ded60cf0ac60d200236b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1442,22 +1410,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.45559</t>
+          <t>156.00221</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>1.6313</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers -0.5</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1482,7 +1450,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1512,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786708080</t>
+          <t>1786708851</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1522,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>26.178142</t>
+          <t>247.132214</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1539,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xe3f456cf1046f05dce10ab68a89684874c657bab224632577bc74065770297f0</t>
+          <t>0x941378707269e8ed5e06a95bc2d98721e8b7ff0eece34bc91f7e8dc6c73dac5d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1554,22 +1522,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20.71654</t>
+          <t>44.97366</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers -0.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1579,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+          <t>Bolton Wanderers vs Preston North End</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0xaab7ad8955da3f0ebc21e85cb94db3fb6514c90829a10cc7307351506de926f4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19292126</t>
+          <t>L19291709</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1624,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786708079</t>
+          <t>1786708757</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786734000</t>
+          <t>1786793400</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>33.346543</t>
+          <t>92.253662</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1651,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x5f84d20a7dcf7c0770fcb2be90eb10bc39423712464a3d757743cb6d8cb9e2b1</t>
+          <t>0x5eb46e0a523b14bdf2cc8cb4828842be713817190b52979b65224fc8dbb37674</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xEf5d1AdDCb6404CDC4496B328c3B2e539b79530d</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1666,12 +1634,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>70.30172</t>
+          <t>3.42999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1736,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786708079</t>
+          <t>1786708273</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1746,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>113.161722</t>
+          <t>5.47703</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1763,7 +1731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x5d406d2e433a065e3651e51153fcac2e5296b8f64049a28000f8ee6ca19472e5</t>
+          <t>0x44f734cd4ef52e63696612eaa384396228698b2f1c2377a4e06f63f581df1a74</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1778,22 +1746,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>163.48</t>
+          <t>141.43332</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers -0.5</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1818,7 +1786,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1848,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786705909</t>
+          <t>1786708085</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1858,7 +1826,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>263.146881</t>
+          <t>224.497333</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1875,7 +1843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x0c77f6a65e164b821e29576416412f928bd09219efb94d2d263c93f5059487a5</t>
+          <t>0xe78d28ff133f41d789623e70ac3fd6613308d9fe8fa93e969c4bf85311232af7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1890,39 +1858,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>211.42</t>
+          <t>7.71294</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>Wolverhampton Wanderers -0.5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -1930,7 +1898,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1960,7 +1928,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786705909</t>
+          <t>1786708082</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1970,7 +1938,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>340.313883</t>
+          <t>12.242762</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1987,23 +1955,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd4f71c2b386f809e90bdc6b4edde9b42d293322d8311378cc3d7ba5d14f4b74e</t>
+          <t>0xc5b5004635526c466c918c6f01bbdbbe1365cb136cdd26badae6c2f34c094f49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>175.94</t>
+          <t>18.61</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2011,7 +1983,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -2064,7 +2040,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786705028</t>
+          <t>1786708082</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2074,7 +2050,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>463.0</t>
+          <t>29.539683</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2091,7 +2067,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x4c3226079a1ff8e01b4bd6cc44c18fe239060b60213810d256ae7d275cb182fa</t>
+          <t>0x6a0a491d3af8142975c3b8281045f72534d93d1c9f4e7286ed87307ede890a58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2099,23 +2075,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28.62999</t>
+          <t>102.98334</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6438</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -2138,7 +2122,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2168,7 +2152,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786705028</t>
+          <t>1786708082</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2178,7 +2162,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>44.473771</t>
+          <t>164.773344</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2195,31 +2179,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x1fcb0a90b5b4b2c89a9d197090ad4cfe7a081725981f9185596083da32f986b2</t>
+          <t>0xd0e875f15c46a885a411e00368a75be2fca469d70066f8fe002453a05e8246e9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>18.45559</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.705</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers 0</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -2242,7 +2234,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2272,7 +2264,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786704432</t>
+          <t>1786708080</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2282,7 +2274,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>72.763158</t>
+          <t>26.178142</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2299,31 +2291,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xf2146c6869444b1914d3c4b2a09ddbdd8baba992f74d87c302595bf00f77b243</t>
+          <t>0x1da64a71c2f3b4f5eb5c0de77dcfeba7a88a1a7dfcc7650ac6ed1c5faf61119d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>18.45559</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.705</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -0.5</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786704199</t>
+          <t>1786708080</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>19.157895</t>
+          <t>26.178142</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2403,7 +2403,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x3c9acadf49f65b4a5d0c9170cf6acd2009a544682f0dc2ca5766e5f793f066a6</t>
+          <t>0xe3f456cf1046f05dce10ab68a89684874c657bab224632577bc74065770297f0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2411,23 +2411,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20.71654</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -0.5</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -2450,7 +2458,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2480,7 +2488,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786704117</t>
+          <t>1786708079</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2490,7 +2498,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>105.263158</t>
+          <t>33.346543</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,7 +2515,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x30471729d0a1f7eda7adce54f1d7444b89ce35023c337a584c031b433ac6c1b3</t>
+          <t>0x5f84d20a7dcf7c0770fcb2be90eb10bc39423712464a3d757743cb6d8cb9e2b1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2515,23 +2523,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.06999</t>
+          <t>70.30172</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -2554,7 +2570,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2584,7 +2600,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786704057</t>
+          <t>1786708079</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2594,7 +2610,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>39.01944</t>
+          <t>113.161722</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2611,7 +2627,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x81c32a23de9c23fb7e3fc10cfdaf7426bb4f68fb17ae4b416f0eb0e9efbc3200</t>
+          <t>0x5d406d2e433a065e3651e51153fcac2e5296b8f64049a28000f8ee6ca19472e5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2619,23 +2635,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>163.48</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -0.5</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -2658,7 +2682,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2688,7 +2712,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786704026</t>
+          <t>1786705909</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2698,7 +2722,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>13.131579</t>
+          <t>263.146881</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,7 +2739,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x1510935dcf3d9a5483bf913ad3bafa3c8af4c94c95bee0144b51dbebeb7488c6</t>
+          <t>0x0c77f6a65e164b821e29576416412f928bd09219efb94d2d263c93f5059487a5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2723,23 +2747,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>211.42</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -2762,7 +2794,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2792,7 +2824,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786704026</t>
+          <t>1786705909</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2802,7 +2834,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>6.588235</t>
+          <t>340.313883</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2819,7 +2851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xaae7fe94b10823331a429059af927d91923beaaa9fa4c3e7ee57cc4ada938f6e</t>
+          <t>0xd4f71c2b386f809e90bdc6b4edde9b42d293322d8311378cc3d7ba5d14f4b74e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2830,7 +2862,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>175.94</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2840,7 +2872,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2866,7 +2898,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2896,7 +2928,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786703492</t>
+          <t>1786705028</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2906,7 +2938,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>3.342105</t>
+          <t>463.0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,7 +2955,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xfc7b428a814a51c4c02fc37ffb48a473de13c1c8f8701be3a8d6b3ada01d1909</t>
+          <t>0x4c3226079a1ff8e01b4bd6cc44c18fe239060b60213810d256ae7d275cb182fa</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2934,17 +2966,17 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>28.62999</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.6438</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2970,7 +3002,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3000,7 +3032,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786703057</t>
+          <t>1786705028</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3042,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>54.938575</t>
+          <t>44.473771</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,28 +3059,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xb9f72195ac3f15f838ea4324736aefcc69c46ac8dbc6951ecf19228296e5bb10</t>
+          <t>0x1fcb0a90b5b4b2c89a9d197090ad4cfe7a081725981f9185596083da32f986b2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>36.99999</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3074,7 +3106,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3104,7 +3136,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786703057</t>
+          <t>1786704432</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3114,7 +3146,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>72.549</t>
+          <t>72.763158</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3131,28 +3163,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x7a815a18f7e224c27b1e002ffe6627439154afa44d1e9209731df034adcdec4a</t>
+          <t>0xf2146c6869444b1914d3c4b2a09ddbdd8baba992f74d87c302595bf00f77b243</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3178,7 +3210,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3208,7 +3240,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786703057</t>
+          <t>1786704199</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3218,7 +3250,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>3.810909</t>
+          <t>19.157895</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3235,7 +3267,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xd38e91420e54dd02160dd7171331660411ce5f42b07e531b202202c04faffc0c</t>
+          <t>0x3c9acadf49f65b4a5d0c9170cf6acd2009a544682f0dc2ca5766e5f793f066a6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3246,17 +3278,17 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3282,7 +3314,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3312,7 +3344,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786702130</t>
+          <t>1786704117</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3322,7 +3354,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>32.586797</t>
+          <t>105.263158</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,7 +3371,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x81d84aa404dde01ed468128eeb16cef67d3c33fa28fcb0713530b58953458b23</t>
+          <t>0x30471729d0a1f7eda7adce54f1d7444b89ce35023c337a584c031b433ac6c1b3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3350,17 +3382,17 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>29.28999</t>
+          <t>25.06999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.8025</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3386,7 +3418,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3416,7 +3448,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786702129</t>
+          <t>1786704057</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3426,7 +3458,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>36.49843</t>
+          <t>39.01944</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,7 +3475,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x022d70e49fee5a6470231c1aec0b8d4f3450c8a3145f42b655bcc8935243ab07</t>
+          <t>0x81c32a23de9c23fb7e3fc10cfdaf7426bb4f68fb17ae4b416f0eb0e9efbc3200</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3451,31 +3483,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2825</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -3498,7 +3522,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3528,7 +3552,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786701768</t>
+          <t>1786704026</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3538,7 +3562,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>19.292035</t>
+          <t>13.131579</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3555,7 +3579,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xca8c0dae8c8d8442cbdefba9afe305367542d83666f8bd708a88324287d71afd</t>
+          <t>0x1510935dcf3d9a5483bf913ad3bafa3c8af4c94c95bee0144b51dbebeb7488c6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3563,31 +3587,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.2825</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -3610,7 +3626,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3640,7 +3656,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786701674</t>
+          <t>1786704026</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3650,7 +3666,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>56.035398</t>
+          <t>6.588235</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3667,7 +3683,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xacbaa8a39ba1ea138e48160ee7a45b4911f00cc50e7e4e7981aa03ebe00b4c78</t>
+          <t>0xaae7fe94b10823331a429059af927d91923beaaa9fa4c3e7ee57cc4ada938f6e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3675,31 +3691,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13.06999</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.6637</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -3722,7 +3730,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3752,7 +3760,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786701314</t>
+          <t>1786703492</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3762,7 +3770,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>19.691134</t>
+          <t>3.342105</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3779,28 +3787,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x09a01c3060df20e13a44f5bb12b7c07356f4ccba498fac22de5f796d559d11af</t>
+          <t>0xfc7b428a814a51c4c02fc37ffb48a473de13c1c8f8701be3a8d6b3ada01d1909</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x3CfEa4e95C4D2ee8C1D790a5a93b2fFbF73F13b4</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3826,7 +3834,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3856,7 +3864,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786701142</t>
+          <t>1786703057</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3866,7 +3874,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.162791</t>
+          <t>54.938575</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3883,18 +3891,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xf522d5120d3a71caa8828427917694e49a4d7017411bae2d26234a35d3b2357a</t>
+          <t>0xb9f72195ac3f15f838ea4324736aefcc69c46ac8dbc6951ecf19228296e5bb10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>305.8</t>
+          <t>36.99999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3960,7 +3968,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786701096</t>
+          <t>1786703057</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3970,7 +3978,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>599.607843</t>
+          <t>72.549</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3987,7 +3995,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xe00843327801b7dfe7c73189f5843a06390d29253719d0c67869963461747dc4</t>
+          <t>0x7a815a18f7e224c27b1e002ffe6627439154afa44d1e9209731df034adcdec4a</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3995,31 +4003,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786700628</t>
+          <t>1786703057</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>72.928571</t>
+          <t>3.810909</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,7 +4099,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x38f49acb11d6eaa4415095ed74edab58a2f97472abdef9ce80c2e9c37db4b7b9</t>
+          <t>0xd38e91420e54dd02160dd7171331660411ce5f42b07e531b202202c04faffc0c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4107,19 +4107,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4127,11 +4123,7 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -4184,7 +4176,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786700628</t>
+          <t>1786702130</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4194,7 +4186,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>63.798995</t>
+          <t>32.586797</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4211,7 +4203,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x0a2d26cefd052e05cedf8048b66edaf09b52415cffd5372843d1894a345fcc6c</t>
+          <t>0x81d84aa404dde01ed468128eeb16cef67d3c33fa28fcb0713530b58953458b23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4222,17 +4214,17 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>29.28999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.8025</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4258,7 +4250,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4288,7 +4280,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786700258</t>
+          <t>1786702129</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4298,7 +4290,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>4.868421</t>
+          <t>36.49843</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,31 +4307,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x2c9def1f3e0afb77fdc953e97cd1727908dcc2d826cbc17cd43e51171437b66d</t>
+          <t>0x022d70e49fee5a6470231c1aec0b8d4f3450c8a3145f42b655bcc8935243ab07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>79.84447</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.2825</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786700040</t>
+          <t>1786701768</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>158.894468</t>
+          <t>19.292035</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,31 +4419,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x35b5a5fe35a66dda4d67b336845c239785184fa94f2aecdffc1cdf1d6962298c</t>
+          <t>0xca8c0dae8c8d8442cbdefba9afe305367542d83666f8bd708a88324287d71afd</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.2825</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -4466,7 +4474,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4496,7 +4504,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786699983</t>
+          <t>1786701674</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4506,7 +4514,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>9.950249</t>
+          <t>56.035398</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4523,31 +4531,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x56723a5c4854e303559eaa9cc9c9bdc538c03e586aa4d84296eb93082f965152</t>
+          <t>0xacbaa8a39ba1ea138e48160ee7a45b4911f00cc50e7e4e7981aa03ebe00b4c78</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13.06999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.6637</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -4570,7 +4586,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4600,7 +4616,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786699982</t>
+          <t>1786701314</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4610,7 +4626,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>9.950249</t>
+          <t>19.691134</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4627,28 +4643,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x988abce096fdbb45c9c2f91ccc82c95d4f973ea1a29e23d5130b5b017a346217</t>
+          <t>0x09a01c3060df20e13a44f5bb12b7c07356f4ccba498fac22de5f796d559d11af</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x3CfEa4e95C4D2ee8C1D790a5a93b2fFbF73F13b4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15.64567</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4674,7 +4690,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4704,7 +4720,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786699978</t>
+          <t>1786701142</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4714,7 +4730,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>31.135662</t>
+          <t>1.162791</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,23 +4747,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x44c9d9e5cf83e7febf6190b7c381059c456fd445e056b017274acf6864ee27a0</t>
+          <t>0xf522d5120d3a71caa8828427917694e49a4d7017411bae2d26234a35d3b2357a</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27.42286</t>
+          <t>305.8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4808,7 +4824,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786699971</t>
+          <t>1786701096</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4818,7 +4834,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>54.572856</t>
+          <t>599.607843</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,31 +4851,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x649c7c2dd52ae0359df126ea1940343017a498a541f372c4b2507c10af20ddfe</t>
+          <t>0xe00843327801b7dfe7c73189f5843a06390d29253719d0c67869963461747dc4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -4882,7 +4906,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4912,7 +4936,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786699912</t>
+          <t>1786700628</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4922,7 +4946,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>9.950249</t>
+          <t>72.928571</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,23 +4963,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x397ed02a9cd89b8e6be27b5b1f56ed7214abf6b23c834c6d97be6573b2889b3e</t>
+          <t>0x38f49acb11d6eaa4415095ed74edab58a2f97472abdef9ce80c2e9c37db4b7b9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>16.39311</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4963,7 +4991,11 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -5016,7 +5048,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786699885</t>
+          <t>1786700628</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5026,7 +5058,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>32.623104</t>
+          <t>63.798995</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5043,7 +5075,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xc541f29064f5649a5c6d31e2f28fa83061ea7eaf3780a787bfbfef2df32f7a8a</t>
+          <t>0x0a2d26cefd052e05cedf8048b66edaf09b52415cffd5372843d1894a345fcc6c</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5054,17 +5086,17 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5090,7 +5122,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5120,7 +5152,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786699877</t>
+          <t>1786700258</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5130,7 +5162,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>41.695761</t>
+          <t>4.868421</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5147,28 +5179,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x7eeb5c48eb7f071d3ad8039a824409bd468add803f4e75b9e9a698a3d89ee01b</t>
+          <t>0x2c9def1f3e0afb77fdc953e97cd1727908dcc2d826cbc17cd43e51171437b66d</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>79.84447</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.6387</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5194,7 +5226,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5224,7 +5256,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786698710</t>
+          <t>1786700040</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5234,7 +5266,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>49.189824</t>
+          <t>158.894468</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5251,28 +5283,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xa297055e4d7f9e759166cb1b5709fe26227c947d0378dad97a400714d9cfd0de</t>
+          <t>0x35b5a5fe35a66dda4d67b336845c239785184fa94f2aecdffc1cdf1d6962298c</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5298,7 +5330,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x0f77092bad3391e566ab01befe9ffbf1d0769f5d84eb4679b9515f28bed1fe92</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5328,7 +5360,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786698376</t>
+          <t>1786699983</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5338,7 +5370,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>9.950249</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5355,28 +5387,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x79d0c0ecbaa602b3ec882bdce9893e23e426a0d1f82e53ea77520c29b593a95e</t>
+          <t>0x56723a5c4854e303559eaa9cc9c9bdc538c03e586aa4d84296eb93082f965152</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>38.91844</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7925</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5402,7 +5434,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5432,7 +5464,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786698376</t>
+          <t>1786699982</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5442,7 +5474,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>49.108442</t>
+          <t>9.950249</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5459,7 +5491,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x5efa6da6dba1830a876144813f77b1056880896f4aecc3a38bd469eeee1c66f1</t>
+          <t>0x988abce096fdbb45c9c2f91ccc82c95d4f973ea1a29e23d5130b5b017a346217</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5470,17 +5502,17 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3.12138</t>
+          <t>15.64567</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5506,7 +5538,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5536,7 +5568,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786698368</t>
+          <t>1786699978</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5546,7 +5578,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>4.925254</t>
+          <t>31.135662</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5563,28 +5595,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xe1caa29bfbdb29c8a7956acbf26da3012c2fe6e7531400a4d751651acb885ac8</t>
+          <t>0x44c9d9e5cf83e7febf6190b7c381059c456fd445e056b017274acf6864ee27a0</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>27.42286</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5610,7 +5642,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5640,7 +5672,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786698367</t>
+          <t>1786699971</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5650,7 +5682,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>44.276134</t>
+          <t>54.572856</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5667,23 +5699,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xc161aa08cd05bf89bc4f4f014dd67c7b5aa50d86b73a618277b58497b22cfa67</t>
+          <t>0x649c7c2dd52ae0359df126ea1940343017a498a541f372c4b2507c10af20ddfe</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5744,7 +5776,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786698366</t>
+          <t>1786699912</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5754,7 +5786,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>81.979798</t>
+          <t>9.950249</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5771,27 +5803,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x45ce743b9508a4f8639ae9c468d4e0cd199ae2a88b650f62ddcdea8e29c6f16b</t>
+          <t>0x397ed02a9cd89b8e6be27b5b1f56ed7214abf6b23c834c6d97be6573b2889b3e</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19.78</t>
+          <t>16.39311</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5799,11 +5827,7 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -5856,7 +5880,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786697734</t>
+          <t>1786699885</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5866,7 +5890,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>38.407767</t>
+          <t>32.623104</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5883,23 +5907,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xd2933a8bedeef87804d4c3e08640d4efc287e3c1cee8ac21be003f5aee5a6271</t>
+          <t>0xc541f29064f5649a5c6d31e2f28fa83061ea7eaf3780a787bfbfef2df32f7a8a</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5960,7 +5984,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786697689</t>
+          <t>1786699877</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5970,7 +5994,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13.699746</t>
+          <t>41.695761</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5987,7 +6011,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xe2cf4a579d0b0e67d6f7cc7f9f3442d5c79ead87f2227e3178d065ff581ece46</t>
+          <t>0x7eeb5c48eb7f071d3ad8039a824409bd468add803f4e75b9e9a698a3d89ee01b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5995,31 +6019,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.75474</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.6387</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -6042,7 +6058,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6072,7 +6088,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786697572</t>
+          <t>1786698710</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6082,7 +6098,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1.465515</t>
+          <t>49.189824</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6099,7 +6115,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x516617c29a1167cdfe89f2778d05e73f8fe78076b679bf83d5e377134bc92c7d</t>
+          <t>0xa297055e4d7f9e759166cb1b5709fe26227c947d0378dad97a400714d9cfd0de</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6107,31 +6123,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -6154,7 +6162,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0x0f77092bad3391e566ab01befe9ffbf1d0769f5d84eb4679b9515f28bed1fe92</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6184,7 +6192,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786697352</t>
+          <t>1786698376</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6194,7 +6202,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>41.184466</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6211,7 +6219,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xda1ca96228df9497ab954525a2cdbcdd7c6bf0555ca0588780d390547adc34c8</t>
+          <t>0x79d0c0ecbaa602b3ec882bdce9893e23e426a0d1f82e53ea77520c29b593a95e</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6219,31 +6227,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>38.91844</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.7925</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786697351</t>
+          <t>1786698376</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>84.110672</t>
+          <t>49.108442</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6323,39 +6323,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xb017477a3f4c28621e50530d3073aaad08b1fa12bd43ef65d7be26ca30a3a5ba</t>
+          <t>0x5efa6da6dba1830a876144813f77b1056880896f4aecc3a38bd469eeee1c66f1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>25.39959</t>
+          <t>3.12138</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.6338</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -6378,7 +6370,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6408,7 +6400,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786697178</t>
+          <t>1786698368</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6418,7 +6410,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>49.319592</t>
+          <t>4.925254</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6435,7 +6427,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xbe27f4cf26acc5ba3b4dc4eaae875e7fc31dc543e83248111299f3f46a291caa</t>
+          <t>0xe1caa29bfbdb29c8a7956acbf26da3012c2fe6e7531400a4d751651acb885ac8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6443,31 +6435,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.00284</t>
+          <t>28.06</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.6837</t>
+          <t>1.6338</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -6490,7 +6474,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
+          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6520,7 +6504,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786696747</t>
+          <t>1786698367</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6530,7 +6514,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>0.004154</t>
+          <t>44.276134</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6547,7 +6531,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xe3d6edfdc1d1866186fd4d81cc85ea388f6588c2393d6646c8a0825499962b14</t>
+          <t>0xc161aa08cd05bf89bc4f4f014dd67c7b5aa50d86b73a618277b58497b22cfa67</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6558,17 +6542,17 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.7875</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6594,7 +6578,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6624,7 +6608,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786696581</t>
+          <t>1786698366</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6634,7 +6618,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>49.269841</t>
+          <t>81.979798</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6651,7 +6635,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xfc3099d2793baeb0f8b54885a6208f4a76afaa9df8adff0585ee986f3ebaef9b</t>
+          <t>0x45ce743b9508a4f8639ae9c468d4e0cd199ae2a88b650f62ddcdea8e29c6f16b</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6666,22 +6650,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>19.78</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.6837</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6706,7 +6690,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6736,7 +6720,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786696574</t>
+          <t>1786697734</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6746,7 +6730,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>44.226691</t>
+          <t>38.407767</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6763,54 +6747,46 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xada31b465a268d17f11a93d18fe728285443b561b9c3ee3b6865950514f09bd4</t>
+          <t>0xd2933a8bedeef87804d4c3e08640d4efc287e3c1cee8ac21be003f5aee5a6271</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>17.35999</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -6818,7 +6794,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6848,7 +6824,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786696515</t>
+          <t>1786697689</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6858,7 +6834,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>27.720543</t>
+          <t>13.699746</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6875,7 +6851,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xc71320352fb6543c55ccfd203e56e89f07c7f8b9f35b1f9d9e20006b4eb032fc</t>
+          <t>0xe2cf4a579d0b0e67d6f7cc7f9f3442d5c79ead87f2227e3178d065ff581ece46</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6890,39 +6866,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>0.75474</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -6930,7 +6906,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6960,7 +6936,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786696238</t>
+          <t>1786697572</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6970,7 +6946,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>124.998004</t>
+          <t>1.465515</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6987,31 +6963,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x3162b1f0fd8b47ccd812d924dc48b9a89c5838a1f10fda6548f6862b67e40507</t>
+          <t>0x516617c29a1167cdfe89f2778d05e73f8fe78076b679bf83d5e377134bc92c7d</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>42.95414</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -7034,7 +7018,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7064,7 +7048,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786696159</t>
+          <t>1786697352</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7074,7 +7058,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>69.84413</t>
+          <t>41.184466</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7091,31 +7075,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x057faa48a6d5fb796cc172e89bcb99aa32240f5df42d2853e82f4476d7088cf6</t>
+          <t>0xda1ca96228df9497ab954525a2cdbcdd7c6bf0555ca0588780d390547adc34c8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>22.63595</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -0.5</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -7138,7 +7130,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7168,7 +7160,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786696159</t>
+          <t>1786697351</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7178,7 +7170,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>72.725944</t>
+          <t>84.110672</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7195,7 +7187,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xd1631d5a15121bf274be8c3bd3b481b3472b97249762cbe235da5d328fd0dc26</t>
+          <t>0xb017477a3f4c28621e50530d3073aaad08b1fa12bd43ef65d7be26ca30a3a5ba</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7210,39 +7202,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>46.23999</t>
+          <t>25.39959</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -7250,7 +7242,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7280,7 +7272,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786696039</t>
+          <t>1786697178</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7290,7 +7282,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>73.836311</t>
+          <t>49.319592</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7307,12 +7299,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xb23eafa1af81eb11286b051397135c536494748b0d78efd2707338c67028c598</t>
+          <t>0xbe27f4cf26acc5ba3b4dc4eaae875e7fc31dc543e83248111299f3f46a291caa</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7322,39 +7314,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.00284</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.6837</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -7362,7 +7354,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7392,7 +7384,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786696000</t>
+          <t>1786696747</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7402,7 +7394,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>7.984032</t>
+          <t>0.004154</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7419,7 +7411,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xcadb075b8681eff2dd984881757d13d4a71dd4454bf6640b2d47e327b7845e21</t>
+          <t>0xe3d6edfdc1d1866186fd4d81cc85ea388f6588c2393d6646c8a0825499962b14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7427,46 +7419,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>31.82999</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.7875</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -7474,7 +7458,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7504,7 +7488,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786695995</t>
+          <t>1786696581</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7514,7 +7498,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>50.826331</t>
+          <t>49.269841</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7531,7 +7515,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x8cfe173093967382e599eca6bcd2204dd0710d009676e1e7dbffec470158655b</t>
+          <t>0xfc3099d2793baeb0f8b54885a6208f4a76afaa9df8adff0585ee986f3ebaef9b</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7546,39 +7530,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>336.9</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.6837</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>The Championship</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
@@ -7586,7 +7570,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7616,7 +7600,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786695994</t>
+          <t>1786696574</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7626,7 +7610,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>537.964072</t>
+          <t>44.226691</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7643,12 +7627,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x41576bc89e013407167df421f0121bbdec867bd666fdf48d94d90d7278325cc2</t>
+          <t>0xada31b465a268d17f11a93d18fe728285443b561b9c3ee3b6865950514f09bd4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7658,7 +7642,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>25.58999</t>
+          <t>17.35999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7728,7 +7712,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786695964</t>
+          <t>1786696515</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7738,7 +7722,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>40.862259</t>
+          <t>27.720543</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7755,7 +7739,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xd08e72d7ae85cc92314f0ad91b14a454f97fcec7144a4824027af0a9de85a9d1</t>
+          <t>0xc71320352fb6543c55ccfd203e56e89f07c7f8b9f35b1f9d9e20006b4eb032fc</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7763,15 +7747,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>145.36999</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.8562</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7779,7 +7767,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -7802,7 +7794,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7832,7 +7824,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786695909</t>
+          <t>1786696238</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7842,7 +7834,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>169.775171</t>
+          <t>124.998004</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7859,28 +7851,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x9fb9c2648330f5ebc76dc05a5634ae196c92970b90848f13af40cddd2da2c406</t>
+          <t>0x3162b1f0fd8b47ccd812d924dc48b9a89c5838a1f10fda6548f6862b67e40507</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>67.13999</t>
+          <t>42.95414</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.6375</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -7906,7 +7898,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7936,7 +7928,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786694046</t>
+          <t>1786696159</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7946,7 +7938,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>105.317631</t>
+          <t>69.84413</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7963,28 +7955,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x9ec955641a39898b90f8fbb0dce44e41b508406ab9613a8157081cf5e1f0e309</t>
+          <t>0x057faa48a6d5fb796cc172e89bcb99aa32240f5df42d2853e82f4476d7088cf6</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>59.56522</t>
+          <t>22.63595</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.8562</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -8010,7 +8002,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8040,7 +8032,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786694045</t>
+          <t>1786696159</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8050,7 +8042,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>69.56522</t>
+          <t>72.725944</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8067,7 +8059,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xeab05b42649eab43e543e45d18f8935b43310f673f71a4f98e13651901cf64ba</t>
+          <t>0xd1631d5a15121bf274be8c3bd3b481b3472b97249762cbe235da5d328fd0dc26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8075,23 +8067,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>46.23999</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786694034</t>
+          <t>1786696039</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>48.065574</t>
+          <t>73.836311</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8171,23 +8171,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xe8d44766130ce5db4c4605cf6edb65cd3897cb44254130f36ddc2347345474cd</t>
+          <t>0xb23eafa1af81eb11286b051397135c536494748b0d78efd2707338c67028c598</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8195,7 +8199,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -8248,7 +8256,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786693662</t>
+          <t>1786696000</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8258,7 +8266,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>7.114094</t>
+          <t>7.984032</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8275,7 +8283,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x044ec0228c6184a02d48e611055043294e7e247ce0e6606fc9a2c52afbc9f8b4</t>
+          <t>0xcadb075b8681eff2dd984881757d13d4a71dd4454bf6640b2d47e327b7845e21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8283,23 +8291,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>31.82999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -8322,7 +8338,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8352,7 +8368,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786693287</t>
+          <t>1786695995</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8362,7 +8378,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>48.065574</t>
+          <t>50.826331</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8379,23 +8395,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x541f717efddc215afed3930ffbd20e8e26480e92678c6057cac813e86768e072</t>
+          <t>0x8cfe173093967382e599eca6bcd2204dd0710d009676e1e7dbffec470158655b</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2.55996</t>
+          <t>336.9</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8403,7 +8423,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -8426,7 +8450,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xe5ad076050ebf08633ea9b91bf5072f3d9a9f79b460dff0451eee48c48db08db</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8456,7 +8480,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786693182</t>
+          <t>1786695994</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8466,7 +8490,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>3.282</t>
+          <t>537.964072</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8483,12 +8507,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x1aff491ef43cc8f1617314673e5a59c3cf888a361714d746bc281a34c069ffe0</t>
+          <t>0x41576bc89e013407167df421f0121bbdec867bd666fdf48d94d90d7278325cc2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8498,22 +8522,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>25.58999</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.4788</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8523,27 +8547,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Sheffield United FC vs Birmingham</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Sheffield United FC</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19291904</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8568,17 +8592,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786692304</t>
+          <t>1786695964</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>1786811400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>19.509138</t>
+          <t>40.862259</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8595,7 +8619,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x036b7f8595fd6db09cd8e408f36f252fd682ee43fc7f48212254eb7b5cbfe1ac</t>
+          <t>0xd08e72d7ae85cc92314f0ad91b14a454f97fcec7144a4824027af0a9de85a9d1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8603,31 +8627,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>19.18788</t>
+          <t>145.36999</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.8562</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -8650,7 +8666,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
+          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8680,7 +8696,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786691340</t>
+          <t>1786695909</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8690,7 +8706,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>49.357891</t>
+          <t>169.775171</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8707,7 +8723,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x65251b41a2200e5bdc20f0829d01ad2f8bd17ecf8b58760d0bd514d9aec2a0e7</t>
+          <t>0x9fb9c2648330f5ebc76dc05a5634ae196c92970b90848f13af40cddd2da2c406</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8718,17 +8734,17 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>13.96857</t>
+          <t>67.13999</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.6375</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -8754,7 +8770,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x0f77092bad3391e566ab01befe9ffbf1d0769f5d84eb4679b9515f28bed1fe92</t>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8784,7 +8800,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786691050</t>
+          <t>1786694046</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8794,7 +8810,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>59.758588</t>
+          <t>105.317631</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8811,7 +8827,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xeef7fdbc6f623362f5b22e9e9851b55a649d3b22d0629618d0399282d976f0f7</t>
+          <t>0x9ec955641a39898b90f8fbb0dce44e41b508406ab9613a8157081cf5e1f0e309</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8822,17 +8838,17 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>59.56522</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.8562</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -8858,7 +8874,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8888,7 +8904,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786690757</t>
+          <t>1786694045</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8898,7 +8914,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>71.181102</t>
+          <t>69.56522</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8915,28 +8931,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xc0f59f7d4f680f2d6c4b15af9fcd33bb40013b8c7213edb06034ffaef8155d62</t>
+          <t>0xeab05b42649eab43e543e45d18f8935b43310f673f71a4f98e13651901cf64ba</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -8947,27 +8963,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xb99abb250b0a6f0129b96f76d74fe24be9e0456e3abe6efb79a30a4b3661122d</t>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19292114</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8992,17 +9008,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786690728</t>
+          <t>1786694034</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>75.83908</t>
+          <t>48.065574</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9019,39 +9035,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x42cc47860d900e2d7e2e19c627d9d9c7d526f0d1557d86261e5d406bdbf99d46</t>
+          <t>0xe8d44766130ce5db4c4605cf6edb65cd3897cb44254130f36ddc2347345474cd</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.6325</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -9074,7 +9082,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9104,7 +9112,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786688827</t>
+          <t>1786693662</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9114,7 +9122,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>7.905123</t>
+          <t>7.114094</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9131,39 +9139,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x8464d57be33ce2f55c677d3da202780847ffdd85c3dfa6a6d80d7ce815105a8c</t>
+          <t>0x044ec0228c6184a02d48e611055043294e7e247ce0e6606fc9a2c52afbc9f8b4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>31.11999</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.6288</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786688817</t>
+          <t>1786693287</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>49.495014</t>
+          <t>48.065574</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9243,39 +9243,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x4667207193cd8c05799c41113eb3fa010abded418c33fb0563c7153e21568351</t>
+          <t>0x541f717efddc215afed3930ffbd20e8e26480e92678c6057cac813e86768e072</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>2.55996</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.3925</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -9298,7 +9290,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
+          <t>0xe5ad076050ebf08633ea9b91bf5072f3d9a9f79b460dff0451eee48c48db08db</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9328,7 +9320,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786688805</t>
+          <t>1786693182</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9338,7 +9330,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>35.057325</t>
+          <t>3.282</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9355,31 +9347,39 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xffdfff603d38c686381000bc91f069bb99d31cebdd19676da11cbf7b164f90f7</t>
+          <t>0x1aff491ef43cc8f1617314673e5a59c3cf888a361714d746bc281a34c069ffe0</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.6987</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -9387,27 +9387,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+          <t>Sheffield United FC vs Birmingham</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sheffield United FC</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
+          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19292126</t>
+          <t>L19291904</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9432,17 +9432,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786688747</t>
+          <t>1786692304</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1786734000</t>
+          <t>1786811400</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>49.159213</t>
+          <t>19.509138</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9459,7 +9459,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x33fde247c5c6973996e8b1fb864ad4efe889ffdbc2841d1b9afab2296d693194</t>
+          <t>0x036b7f8595fd6db09cd8e408f36f252fd682ee43fc7f48212254eb7b5cbfe1ac</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9467,23 +9467,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>19.18788</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.4737</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -9506,7 +9514,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9536,7 +9544,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786688747</t>
+          <t>1786691340</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9546,7 +9554,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>35.313984</t>
+          <t>49.357891</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9563,7 +9571,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x56b12908d45a0a6d124c5eba50f10571c241cba2a831d338dd1abd9b46538145</t>
+          <t>0x65251b41a2200e5bdc20f0829d01ad2f8bd17ecf8b58760d0bd514d9aec2a0e7</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9571,31 +9579,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>13.96857</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
+          <t>0x0f77092bad3391e566ab01befe9ffbf1d0769f5d84eb4679b9515f28bed1fe92</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786688148</t>
+          <t>1786691050</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>19.46988</t>
+          <t>59.758588</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9675,28 +9675,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xc7dd73efc8a2687272b80e45be086997d0a80191961ab64cecfa57daa1f2f22e</t>
+          <t>0xeef7fdbc6f623362f5b22e9e9851b55a649d3b22d0629618d0399282d976f0f7</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>13.80271</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -9707,27 +9707,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9752,17 +9752,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786687562</t>
+          <t>1786690757</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>21.032701</t>
+          <t>71.181102</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9779,28 +9779,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x1fa03bf72cff6dce4d0ea2e6afe0c3c4d96e870ad881c829d4b280526f52994d</t>
+          <t>0xc0f59f7d4f680f2d6c4b15af9fcd33bb40013b8c7213edb06034ffaef8155d62</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>48.6786</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.6362</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>The Championship</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -9811,27 +9811,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+          <t>Portsmouth vs Queens Park Rangers</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+          <t>0xb99abb250b0a6f0129b96f76d74fe24be9e0456e3abe6efb79a30a4b3661122d</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19292126</t>
+          <t>L19292114</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9856,17 +9856,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786687154</t>
+          <t>1786690728</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>1786734000</t>
+          <t>1786802400</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>76.508605</t>
+          <t>75.83908</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9883,31 +9883,39 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x2181f862594910f0be2837965261ee46675dcd94fd6477edde8e2ef6700a3620</t>
+          <t>0x42cc47860d900e2d7e2e19c627d9d9c7d526f0d1557d86261e5d406bdbf99d46</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>28.93998</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.8525</t>
+          <t>1.6325</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -0.5</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -9930,7 +9938,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9960,7 +9968,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786686832</t>
+          <t>1786688827</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9970,7 +9978,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>33.947191</t>
+          <t>7.905123</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9987,12 +9995,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x9a30cb693b24b6af0b636876c34b3721ed6c64f547308b4491fe3874711d6390</t>
+          <t>0x8464d57be33ce2f55c677d3da202780847ffdd85c3dfa6a6d80d7ce815105a8c</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10002,22 +10010,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31.11999</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.6288</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Wolverhampton Wanderers -0.5</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -10042,7 +10050,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10072,7 +10080,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1786686792</t>
+          <t>1786688817</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10082,7 +10090,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>7.407407</t>
+          <t>49.495014</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10099,12 +10107,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x5cf303c4268c205c3900dd177e853e57be65f604c6cf2f75bb3ec158206319e8</t>
+          <t>0x4667207193cd8c05799c41113eb3fa010abded418c33fb0563c7153e21568351</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0xc1BEa02928E7Dbb4b88c093f3EFC8FEcdC54334f</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10114,22 +10122,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.3925</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10154,7 +10162,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0xe5ad076050ebf08633ea9b91bf5072f3d9a9f79b460dff0451eee48c48db08db</t>
+          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10184,7 +10192,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1786686289</t>
+          <t>1786688805</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10194,7 +10202,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>186.813187</t>
+          <t>35.057325</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10211,7 +10219,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x85bc4c2b09a29cb7b51361cb6e00c779b54c2ba9aa0fa910571efb4334c34a34</t>
+          <t>0xffdfff603d38c686381000bc91f069bb99d31cebdd19676da11cbf7b164f90f7</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10219,31 +10227,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.2188</t>
+          <t>1.6987</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers -2</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1786684350</t>
+          <t>1786688747</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>46.354286</t>
+          <t>49.159213</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10323,7 +10323,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0xe421855f5800b15e1ce538ac99e357340482a63f9eb53861728bf1fe6f5927ef</t>
+          <t>0x33fde247c5c6973996e8b1fb864ad4efe889ffdbc2841d1b9afab2296d693194</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10331,31 +10331,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.2188</t>
+          <t>1.4737</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers -2</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -10378,7 +10370,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10408,7 +10400,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1786681813</t>
+          <t>1786688747</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10418,7 +10410,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>13.485714</t>
+          <t>35.313984</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10435,7 +10427,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xdfd3b0e87b38a21c6b6de5e710fa222376f415690d024b88ddc6ac78e8ffd6a2</t>
+          <t>0x56b12908d45a0a6d124c5eba50f10571c241cba2a831d338dd1abd9b46538145</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10443,23 +10435,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>35.36889</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
+          <t>0xd3225720482236241bf45a985c4e72085d3f514b463d39920b8b03eb8df001ed</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1786681421</t>
+          <t>1786688148</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>59.318893</t>
+          <t>19.46988</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10539,28 +10539,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x90a0e7eda8f358bfbc693c5b170d49b5b82643edb5226d7baf7c5efb116e35f4</t>
+          <t>0xc7dd73efc8a2687272b80e45be086997d0a80191961ab64cecfa57daa1f2f22e</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>13.80271</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -10571,27 +10571,27 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+          <t>Bolton Wanderers vs Preston North End</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
+          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>L19292126</t>
+          <t>L19291709</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -10616,17 +10616,17 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1786681421</t>
+          <t>1786687562</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>1786734000</t>
+          <t>1786793400</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>66.194093</t>
+          <t>21.032701</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10643,7 +10643,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0xf07ac8a6314c65b6d3fa4324af4db0742f2b81142e826d79c02967ae2b680845</t>
+          <t>0x1fa03bf72cff6dce4d0ea2e6afe0c3c4d96e870ad881c829d4b280526f52994d</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10654,17 +10654,17 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>48.6786</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.6362</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1786681420</t>
+          <t>1786687154</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>62.287263</t>
+          <t>76.508605</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10747,7 +10747,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0xee5c5a9e51e535e869e916990033cb897db812220c0aac5432bf2226c3d7ee57</t>
+          <t>0x2181f862594910f0be2837965261ee46675dcd94fd6477edde8e2ef6700a3620</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10758,17 +10758,17 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>48.17</t>
+          <t>28.93998</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.7738</t>
+          <t>1.8525</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1786681101</t>
+          <t>1786686832</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>62.25525</t>
+          <t>33.947191</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10851,31 +10851,39 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x79e08f4bc06434a4f7979320414002d9965fb48cb9bc37896538f9f823d71572</t>
+          <t>0x9a30cb693b24b6af0b636876c34b3721ed6c64f547308b4491fe3874711d6390</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>18.73305</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -10898,7 +10906,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10928,7 +10936,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1786681101</t>
+          <t>1786686792</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10938,7 +10946,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>29.913054</t>
+          <t>7.407407</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10955,31 +10963,39 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0x1d5be24f030cf08ecf8f855e19663320ae258826d7bb9f9b58cb44aa00e0d704</t>
+          <t>0x5cf303c4268c205c3900dd177e853e57be65f604c6cf2f75bb3ec158206319e8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>0xc1BEa02928E7Dbb4b88c093f3EFC8FEcdC54334f</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.2275</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -11002,7 +11018,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0xe5ad076050ebf08633ea9b91bf5072f3d9a9f79b460dff0451eee48c48db08db</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -11032,7 +11048,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1786681101</t>
+          <t>1786686289</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11042,7 +11058,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>105.188917</t>
+          <t>186.813187</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11059,7 +11075,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0x47a0705d873daff1b9735c7743adc7d7070905bee2a7f19cf8b07326af3af9ce</t>
+          <t>0x85bc4c2b09a29cb7b51361cb6e00c779b54c2ba9aa0fa910571efb4334c34a34</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11074,22 +11090,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>22.33999</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.2188</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Wolverhampton Wanderers -2</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11114,7 +11130,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -11144,7 +11160,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1786678335</t>
+          <t>1786684350</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11154,7 +11170,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>31.299461</t>
+          <t>46.354286</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11171,7 +11187,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0x0eed25f538f3923c390dcdeb951387eab37a7b6903d2ff32be765d4c2b578176</t>
+          <t>0xe421855f5800b15e1ce538ac99e357340482a63f9eb53861728bf1fe6f5927ef</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11179,23 +11195,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>62.24994</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.8562</t>
+          <t>1.2188</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers -2</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -11218,7 +11242,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -11248,7 +11272,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1786672368</t>
+          <t>1786681813</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11258,7 +11282,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>72.70066</t>
+          <t>13.485714</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11275,7 +11299,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0x1ca5645b840e0099c37a192c12665c34258dca551f75cca08585650a1b8119c5</t>
+          <t>0xdfd3b0e87b38a21c6b6de5e710fa222376f415690d024b88ddc6ac78e8ffd6a2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11286,17 +11310,17 @@
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>35.36889</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.4663</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -11322,7 +11346,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
+          <t>0xa767857d543cf3fdb5c77a5bac3dc1f48cecc20f6855ed981494393f8ea2ba24</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -11352,7 +11376,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1786654867</t>
+          <t>1786681421</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11362,7 +11386,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>22.841823</t>
+          <t>59.318893</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11379,7 +11403,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0xf866368b051fe0cbdd3da4934c3bc39714b17f0249c765c085c864368ae0c2d9</t>
+          <t>0x90a0e7eda8f358bfbc693c5b170d49b5b82643edb5226d7baf7c5efb116e35f4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11387,31 +11411,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>10.59988</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Wolverhampton Wanderers -2</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -11434,7 +11450,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -11464,7 +11480,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1786651979</t>
+          <t>1786681421</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11474,7 +11490,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>47.63991</t>
+          <t>66.194093</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11491,7 +11507,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0xa30b5de275cc97dc98ab7b990de9244cc76a5cd746f5e91690bc2938ce24c906</t>
+          <t>0xf07ac8a6314c65b6d3fa4324af4db0742f2b81142e826d79c02967ae2b680845</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11502,17 +11518,17 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -11538,7 +11554,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -11568,7 +11584,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>1786651979</t>
+          <t>1786681420</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11578,7 +11594,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>7.367742</t>
+          <t>62.287263</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11595,28 +11611,28 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0xd52581c04ad82aa50dd0e5fd34c05139f4741fac293b4131701be67fa1f4e9fd</t>
+          <t>0xee5c5a9e51e535e869e916990033cb897db812220c0aac5432bf2226c3d7ee57</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>29.57257</t>
+          <t>48.17</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.7738</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -11642,7 +11658,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -11672,7 +11688,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>1786637737</t>
+          <t>1786681101</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11682,7 +11698,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>59.742566</t>
+          <t>62.25525</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11699,28 +11715,28 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0x830f9a73e2c448c31ca55665eabaac552ea63303de6c11ee3218137ca19171c3</t>
+          <t>0x79e08f4bc06434a4f7979320414002d9965fb48cb9bc37896538f9f823d71572</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>18.73305</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.6262</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -11746,7 +11762,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -11776,7 +11792,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>1786636199</t>
+          <t>1786681101</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -11786,7 +11802,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>45.849246</t>
+          <t>29.913054</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -11803,28 +11819,28 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0xe3095a8d8520173ca9ca0e37b8915f9befbcf19766b6d15861b56a62fd451312</t>
+          <t>0x1d5be24f030cf08ecf8f855e19663320ae258826d7bb9f9b58cb44aa00e0d704</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>15.37331</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.1912</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -11850,7 +11866,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -11880,7 +11896,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786681101</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11890,7 +11906,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>80.38332</t>
+          <t>105.188917</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -11907,31 +11923,39 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0xd6836273ea70f65f0163c9825f8b5f82c746330452f7d9529c96a87e10fde671</t>
+          <t>0x47a0705d873daff1b9735c7743adc7d7070905bee2a7f19cf8b07326af3af9ce</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>53.10381</t>
+          <t>22.33999</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -11954,7 +11978,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0x0b4a88abf27227ade1daac1b986112f3adcab5665b834237a1114ba8207a922a</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -11984,7 +12008,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786678335</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -11994,7 +12018,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>143.523811</t>
+          <t>31.299461</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12011,28 +12035,28 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0x9b861e3a5951a5bc4a795bbd4936d267f07999dfdbc8680041a8afb95a853d63</t>
+          <t>0x0eed25f538f3923c390dcdeb951387eab37a7b6903d2ff32be765d4c2b578176</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>15.37331</t>
+          <t>62.24994</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1.1912</t>
+          <t>1.8562</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>The Championship</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -12058,7 +12082,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>0x6c28e6d44aba4a5c5135538948c11f026030c3793c5b485a1fddac009874d97c</t>
+          <t>0xd1cc37e440b7466bb55cda27a9a743ef29f88d223cc6b4fda2544281bb856ad7</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -12088,7 +12112,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786672368</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -12098,7 +12122,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>80.38332</t>
+          <t>72.70066</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -12115,28 +12139,28 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0x4c8f7a1fd16abd3821389519299c565b87c1cfc798c8f40cba30cb98d1cb3a8e</t>
+          <t>0x1ca5645b840e0099c37a192c12665c34258dca551f75cca08585650a1b8119c5</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.4663</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -12162,7 +12186,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
+          <t>0x66b4718d2fa5a5bd46cb252bbdf9806922c5b1a42e8c219b5a1be6fd994da6eb</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -12192,7 +12216,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>1786633531</t>
+          <t>1786654867</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -12202,7 +12226,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>22.841823</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -12219,12 +12243,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0x29a09089970963ba620d5e0ec4f16a2c200278f6312c796968ef3083a5788664</t>
+          <t>0xf866368b051fe0cbdd3da4934c3bc39714b17f0249c765c085c864368ae0c2d9</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12234,22 +12258,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>10.59988</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.3413</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Wolverhampton Wanderers -2</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12259,27 +12283,27 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>0x434e450484615c8151c89575c12a656ce79bf52c262db30f4d9d1711975a5a43</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>L19292114</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -12304,17 +12328,17 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>1786629015</t>
+          <t>1786651979</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>38.358974</t>
+          <t>47.63991</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12331,28 +12355,28 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0x537be368ed5c10f96c004f82bf70d830d895e83a27d307988ebb471734297180</t>
+          <t>0xa30b5de275cc97dc98ab7b990de9244cc76a5cd746f5e91690bc2938ce24c906</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>15.15832</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -12378,7 +12402,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
+          <t>0x2edfb4eb3f5dde113a5812aac926e402ff0c53cf035db8cd648e8794b852796f</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -12408,7 +12432,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1786625324</t>
+          <t>1786651979</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -12418,7 +12442,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>30.778315</t>
+          <t>7.367742</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -12435,7 +12459,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0x0baa6a9ec22c5ea443e8ee1130a9e8d7d9b9fa0084f51b5e1ee100ac5168a69d</t>
+          <t>0xd52581c04ad82aa50dd0e5fd34c05139f4741fac293b4131701be67fa1f4e9fd</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12446,17 +12470,17 @@
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>42.72887</t>
+          <t>29.57257</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -12482,7 +12506,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -12512,7 +12536,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>1786625324</t>
+          <t>1786637737</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -12522,7 +12546,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>68.778865</t>
+          <t>59.742566</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -12539,7 +12563,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
+          <t>0x830f9a73e2c448c31ca55665eabaac552ea63303de6c11ee3218137ca19171c3</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12547,31 +12571,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Queens Park Rangers</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -12579,27 +12595,27 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>L19292114</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -12624,17 +12640,17 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>1786621774</t>
+          <t>1786636199</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>139.699605</t>
+          <t>45.849246</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -12651,39 +12667,31 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
+          <t>0xe3095a8d8520173ca9ca0e37b8915f9befbcf19766b6d15861b56a62fd451312</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>19.99999</t>
+          <t>15.37331</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.1912</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -12691,27 +12699,27 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Portsmouth vs Queens Park Rangers</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
+          <t>0x71a45e06b8c9e8ad5d7364d520435d71e9686fa05cc6f0bcf4e52d6ed08acfc0</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>L19292114</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12736,17 +12744,17 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>1786619915</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>26.890743</t>
+          <t>80.38332</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -12763,39 +12771,31 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
+          <t>0xd6836273ea70f65f0163c9825f8b5f82c746330452f7d9529c96a87e10fde671</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>53.10381</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1.4863</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -12803,27 +12803,27 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Sheffield United FC vs Birmingham</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Sheffield United FC</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>L19291904</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12848,17 +12848,17 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>1786615902</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>1786811400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>16.781491</t>
+          <t>143.523811</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -12875,23 +12875,23 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
+          <t>0x9b861e3a5951a5bc4a795bbd4936d267f07999dfdbc8680041a8afb95a853d63</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>50.81</t>
+          <t>15.37331</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1.4575</t>
+          <t>1.1912</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -12907,27 +12907,27 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Stoke City vs Swansea City</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
+          <t>0x6c28e6d44aba4a5c5135538948c11f026030c3793c5b485a1fddac009874d97c</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>L19291703</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -12952,17 +12952,17 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>1786609224</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>1786802400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>111.060109</t>
+          <t>80.38332</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -12979,28 +12979,28 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
+          <t>0x4c8f7a1fd16abd3821389519299c565b87c1cfc798c8f40cba30cb98d1cb3a8e</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1.3692</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+          <t>0xba0ac81588abc1e0d093cf39f851801ab8050d0e31be3e8ed3e67f0244586d14</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>1786606182</t>
+          <t>1786633531</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>3.725714</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -13083,7 +13083,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
+          <t>0x29a09089970963ba620d5e0ec4f16a2c200278f6312c796968ef3083a5788664</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13091,23 +13091,31 @@
           <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1.8662</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>The Championship</t>
@@ -13115,27 +13123,27 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Portsmouth vs Queens Park Rangers</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
+          <t>0x434e450484615c8151c89575c12a656ce79bf52c262db30f4d9d1711975a5a43</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19292114</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -13160,17 +13168,17 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>1786593406</t>
+          <t>1786629015</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786802400</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>16.519481</t>
+          <t>38.358974</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13187,28 +13195,28 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+          <t>0x537be368ed5c10f96c004f82bf70d830d895e83a27d307988ebb471734297180</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>12.51999</t>
+          <t>15.15832</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -13219,27 +13227,27 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Bolton Wanderers vs Preston North End</t>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+          <t>0xe934fe1cff54117e2f89af87a62cffd7a9c5c64ac1039abf0be172154dc8671a</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>L19291709</t>
+          <t>L19292126</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -13264,17 +13272,17 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>1786593405</t>
+          <t>1786625324</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>1786793400</t>
+          <t>1786734000</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>18.548133</t>
+          <t>30.778315</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -13291,110 +13299,966 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>0x0baa6a9ec22c5ea443e8ee1130a9e8d7d9b9fa0084f51b5e1ee100ac5168a69d</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>42.72887</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1.6212</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>0xa0e7467be450fdf8f03c5c39b4f2d1177ae9b976a890667df0b58a9b7f963d7e</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>1786625324</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>68.778865</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>0xdd833a3a4c19eb8bedcbb99d94ca3ba8f3254f43f313ec5941d68f7b03cd9760</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>44.18</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1.3162</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>0x8cb123b30c438380831a29f7f00ebfefe2417a8377eb1f901e47530bfb8e3607</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>L19292114</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>1786621774</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>139.699605</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>0x8d014d702daa0fec2796de61faa00a5a489f4456da1bc5d727469b9626dcfa2e</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>19.99999</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1.7437</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>0xf7d5c2489939df1ac031aef3a884c918571f25d0222b098246709a271051ed09</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>L19292114</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>1786619915</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>26.890743</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>0x0a0f5d3ceb3b0e2c1a8b08dbc92957d75b77d0d6bd034809f013928a367c050a</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>8.16</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1.4863</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Sheffield United FC vs Birmingham</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Sheffield United FC</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>0x5282da2c3d8ffd28231068160b4889f9e8bd02717996d16d975fcf0044b4ee9f</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>L19291904</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>1786615902</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>1786811400</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>16.781491</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>0x09e8e958f591a8662933ea275c19a463453b8b3f0999a43667c16520cb90d753</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>50.81</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1.4575</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Stoke City vs Swansea City</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>0x362303ed7f21a1245ae42d143cfe5ad64f98a78cd65c20abf00d69a0800afdf1</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>L19291703</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>1786609224</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>1786802400</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>111.060109</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>0xec61705e08403d173820c91af89ce93f6f370b4c811eb44e3afde579f922cf45</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1.3692</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1.3675</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>0xb567187d84b0149a385592d343101818e8a3038602155d5229929da2b6897a2d</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>L19292126</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>1786606182</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>1786734000</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>3.725714</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>0x401ffd4e5e2543185bc96d1aadd566c1590d53689798404ed8aa42af95e5121e</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>14.31</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1.8662</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>0x2ff4d5e3f2721ae93d3218755554dab7f363623ab4979351e4a88fc4afd92b19</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>1786593406</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>16.519481</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>0x87dfb24dcef66e5f661b520694b069307554aa793fe5fdaed55eb16c78ddbf88</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>12.51999</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1.675</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>The Championship</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>0x8b6e240648995ba512bea2530057610f52e525c7cf1b323d2236ee1422e49843</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>L19291709</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>1786593405</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>1786793400</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>18.548133</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>0x70c4d883377e0e7a1da0f5a54162f0682a7a75df864f08a0d9215d9bc3d1bb50</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
         <is>
           <t>4.99998</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>Over 1.5</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>The Championship</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers vs Blackburn Rovers</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t>Wolverhampton Wanderers</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="K129" t="inlineStr">
         <is>
           <t>Blackburn Rovers</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t>0x0f77092bad3391e566ab01befe9ffbf1d0769f5d84eb4679b9515f28bed1fe92</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t>L19292126</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr">
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
         <is>
           <t>1786496850</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
+      <c r="S129" t="inlineStr">
         <is>
           <t>1786734000</t>
         </is>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="T129" t="inlineStr">
         <is>
           <t>6.410231</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="U129" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V121" t="inlineStr">
+      <c r="V129" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
